--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_005/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_005/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -449,11 +454,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G4" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -564,12 +564,57 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
     <comment ref="I7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1331,7 +1376,7 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Steady-state conjugate heat transfer model of a cold plate module hosting six IGBTs on a copper baseplate bolted to a machined aluminum serpentine-channel cold plate with EGW 50/50 coolant. Results inform mechanical layout, pump sizing, and guardbands on allowable inlet temperature and flow rate for the thermal-fluid loop. Power levels 300–600 W, mass flow 0.08–0.20 kg/s, inlet temperature 10–35 C.</t>
+          <t>Steady-state conjugate heat transfer model of a single cold plate module hosting six IGBTs on a copper baseplate bolted to a machined aluminum serpentine-channel cold plate. Results used to set guardbands on allowable inlet temperature and flow rate for the thermal-fluid loop, and to inform mechanical layout and pump sizing. Valid for 300–600 W total die power, 0.08–0.20 kg/s flow, 10–35 C inlet temperature.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1369,9 +1414,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md; appendix.md (PCU Cold Plate for EPS Rack, CP-CHT-v1.6, dated 2026-08-05)</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1500,7 +1545,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Model must predict peak die junction temperature within ~2 C and coolant-side pressure drop within ~5% of measured values to support setting allowable inlet temperature and flow rate guardbands and preliminary pump sizing decisions.</t>
+          <t>Model must predict peak die junction temperature within ~2 C and pressure drop within ~5% of measured bench values to support setting of allowable inlet temperature and flow rate guardbands for early design trades and pump sizing.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1522,12 +1567,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>CP-CHT-v1.6 Conjugate Heat Transfer Model</t>
+          <t>CP-CHT-v1.6</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>3D steady-state conjugate thermal-fluid model in STAR-CCM+ 2023.1.2 with SST k-omega turbulence, poly-hexcore mesh (31.4M cells fine level), EGW 50/50 fluid properties, and TIM contact conductance from in-house measurement.</t>
+          <t>3D conjugate heat transfer RANS model in STAR-CCM+ 2023.1.2 with SST k-omega turbulence, covering fluid and solid domains of the PCU cold plate.</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1584,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Bench Test Dataset — Coupon Cold Plate BenchA 2026Q2</t>
+          <t>Bench Test Dataset — BenchA 2026Q2</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Thermocouple, RTD, pressure transducer, and IR thermography measurements from instrumented coupon cold plate at three flow rates (0.09, 0.12, 0.16 kg/s) and two power settings (300, 450 W) at ~20 C inlet temperature.</t>
+          <t>Coupon-level cold plate bench measurements: 12 surface thermocouples, 2 RTDs, inlet/outlet pressure transducers, IR thermography; tested at 300 W and 450 W, three flow rates, ~20 C inlet.</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1601,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>TIM Conductance Measurement Data</t>
+          <t>TIM Conductance Measurement Dataset</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>In-house guarded heat flow meter measurements of TIM thermal contact conductance at 40, 60, and 80 C under 0.3 MPa clamping force; used as interpolated boundary input to the CHT model.</t>
+          <t>In-house guarded heat flow meter measurements of TIM thermal contact conductance at 40, 60, and 80 C under 0.3 MPa clamping force; interpolated to 65 C for analysis.</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1618,12 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Material and Fluid Property Sources</t>
+          <t>Material Properties Dataset</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>EGW 50/50 properties from ASHRAE Fundamentals 2021 cross-checked against NIST REFPROP; 6061-T6 aluminum conductivity from vendor cert (167±5 W/m-K); C110 copper and TIM/dielectric pad properties from vendor datasheets.</t>
+          <t>Temperature-dependent fluid properties for EGW 50/50 from ASHRAE and cross-checked against NIST REFPROP; 6061-T6 aluminum k from vendor cert; copper and TIM properties from vendor datasheets.</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2015,7 +2060,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Temperature Comparison — 450 W, 0.12 kg/s Nominal Case</t>
+          <t>Mesh Convergence / Grid Sensitivity Study</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2030,12 +2075,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Predicted surface temperatures at six instrumented die corners compared against K-type thermocouple measurements and IR thermography cross-check at the nominal operating point (450 W, 0.12 kg/s, ~20 C inlet).</t>
+          <t>Three mesh levels (coarse 11.2M, medium 18.7M, fine 31.4M cells) run at nominal conditions (450 W, 0.12 kg/s, 20 C). Peak die temperatures: 79.5 / 78.7 / 78.4 C. Richardson extrapolation gives asymptotic estimate 78.2 C; change fine-to-extrapolated 0.2 C (0.26%). Pressure drop changed 0.8 kPa between medium and fine (4.1%).</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>12 surface thermocouples (K-type 36 AWG) and emissivity-corrected IR thermography on coupon cold plate</t>
+          <t>Richardson-extrapolated asymptotic solution</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2045,12 +2090,12 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Measurement uncertainty reported (inlet temperature ±0.3 C); probabilistic LHS (200 samples) provides model output uncertainty (σ = 0.95 C, 90th percentile T_max = 81.1 C)</t>
+          <t>Monotonic convergence extrapolation (Richardson)</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>Average absolute temperature difference 1.9 C; maximum single-point deviation 3.4 C at upstream corner of D2</t>
+          <t>T_max fine-to-extrapolated: 0.2 C (0.26%); ΔP medium-to-fine: 0.8 kPa (4.1%)</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2062,7 +2107,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Pressure Drop Comparison — 450 W, 0.12 kg/s Nominal Case</t>
+          <t>Solver Convergence and Energy Balance Check</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2072,27 +2117,22 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Predicted inlet-to-outlet pressure drop compared against calibrated 0–3 bar transducer measurements at the nominal operating point.</t>
+          <t>Normalized residuals reached &lt;1e-5 for all equations over 2,000 iterations on all envelope cases. Energy imbalance decreased from 1.2% at 500 iterations to 0.08% at 2,000 iterations (nominal, medium mesh). Mass imbalance &lt;0.2% for all runs. Fluid-solid interface heat flux agreement within 0.15% at convergence.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Calibrated pressure transducers (linearity ±0.25% FS, calibrated week-of-test against DPI 620 calibrator)</t>
+          <t>Convergence criteria thresholds (residuals &lt;1e-5, energy imbalance &lt;0.1%)</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Transducer measurement uncertainty (±0.5 kPa reported); LHS 90th percentile ΔP = 20.3 kPa</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>Model 18.7 kPa vs. measured 19.6±0.5 kPa; 4.6% underprediction</t>
+          <t>Energy imbalance 0.08%; interface heat flux agreement 0.15%; residuals &lt;1e-5</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2104,7 +2144,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Temperature Comparison — 300 W, 0.09 kg/s and 300 W, 0.16 kg/s Cases</t>
+          <t>Code Verification — 1D Conduction Analytical Benchmark</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2114,12 +2154,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Model temperature predictions compared against thermocouple measurements at 300 W total power across two flow rates, assessing prediction fidelity away from the nominal operating point.</t>
+          <t>Conduction-only model of a 1D slab with imposed heat flux compared against analytical temperature profile.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Surface thermocouple measurements on coupon cold plate bench</t>
+          <t>Analytical solution for 1D heat conduction slab</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2129,7 +2169,7 @@
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>300 W, 0.09 kg/s: model overpredicts hottest TC by 2.3 C; 0.16 kg/s: average difference &lt;1.5 C</t>
+          <t>Agreement within 0.1 C</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2141,7 +2181,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Mesh Convergence Study — Peak Junction Temperature and Pressure Drop</t>
+          <t>Temperature Comparison to Bench Measurements</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2151,12 +2191,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Three-level mesh refinement study (coarse 11.2M, medium 18.7M, fine 31.4M cells) at nominal conditions to assess discretization error in T_max and pressure drop.</t>
+          <t>Model-predicted surface temperatures at six instrumented die corners compared to K-type thermocouple measurements from bench test at 450 W, 0.12 kg/s, ~20 C inlet. Also compared at 300 W / 0.09 kg/s and 450 W / 0.16 kg/s conditions. IR thermography used to cross-check two TC locations.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / monotonic convergence asymptote</t>
+          <t>Bench thermocouple and IR thermography measurements</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2166,12 +2206,12 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Monotonic convergence extrapolation; estimated asymptotic T_max = 78.2 C</t>
+          <t>Measurement uncertainty quoted (inlet temperature ±0.3 C); instrument calibration documented</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Fine-to-extrapolated T_max change 0.2 C (0.26%); medium-to-fine ΔP change 0.8 kPa (4.1%)</t>
+          <t>Average absolute error 1.9 C (450 W nominal); max single-point deviation 3.4 C; at 300 W/0.09 kg/s overprediction 2.3 C; at 0.16 kg/s average &lt;1.5 C</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2183,7 +2223,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Code Verification — 1-D Conduction Slab Analytical Benchmark</t>
+          <t>Pressure Drop Comparison to Bench Measurements</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2193,25 +2233,72 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Conduction-only model of a 1-D slab with imposed heat flux compared against analytical temperature profile to verify STAR-CCM+ energy equation implementation.</t>
+          <t>Predicted inlet-to-outlet pressure drop (18.7 kPa) compared to measured value (19.6±0.5 kPa) at 450 W, 0.12 kg/s nominal condition.</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Analytical solution for 1-D slab conduction</t>
+          <t>Calibrated pressure transducer measurements (DPI 620 calibrator, linearity ±0.25% FS)</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>Instrument calibration uncertainty (±0.5 kPa stated on measurement)</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>Temperature profile match within 0.1 C</t>
+          <t>4.6% underprediction (18.7 vs 19.6 kPa)</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Probabilistic Uncertainty Quantification (LHS)</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>ValidationResult</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Latin Hypercube Sampling with 200 runs on medium mesh at nominal conditions. Uncertain inputs: inlet temperature, mass flow, TIM conductance, aluminum conductivity, die power (with inter-device correlation). Output distributions for T_max and pressure drop computed; Sobol sensitivity indices estimated via rank regression.</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Deterministic nominal prediction and component-level requirements</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Latin Hypercube Sampling (200 samples), Sobol index approximation via rank regression</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>T_max 90th percentile 81.1 C; mean 78.9 C; std dev 0.95 C; ΔP 90th percentile 20.3 kPa</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2362,12 +2449,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Commercial solver used with documented version and reproducibility evidence</t>
+          <t>Evidence of solver version control, reproducibility, and configuration management for commercial CFD code</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>STAR-CCM+ 2023.1.2 (build 17.06.007) is a well-established commercial CFD solver. All input decks, macros, and property files are under version control (Git LFS) tagged at cp-cht-1.6.0. File hash checksums (SHA-256) are generated at solver launch and archived in SharePoint with a manifest. Re-run on a second compute node (EPYC 7543) reproduced T_max within 0.07 C and ΔP within 0.3 kPa. Results are reproducible to within 0.05 C on the reference node. No explicit ISO/IEC 9001 certification or regression test suite is cited for the solver itself.</t>
+          <t>STAR-CCM+ 2023.1.2 (build 17.06.007) is a commercial solver with an identified version and build number. Pre-processing and solver settings are scripted via committed Java macros (cp-cht-1.6.0 tag). File hashes (SHA-256) for geometry, material properties, and power input files are recorded and checked at solver launch; mismatches flagged in run log. Re-run on a second node (EPYC 7543) produced T_max within 0.07 C and ΔP within 0.3 kPa. Results archived on SharePoint with checksums. No explicit ISO certification or formal regression test suite for the solver itself is cited, limiting the level.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2389,19 +2476,19 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Code correctly solves governing equations, demonstrated by comparison to analytical solution</t>
+          <t>Evidence that the code correctly solves the governing equations, e.g., comparison to analytical solutions or benchmark problems</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>A conduction-only 1-D slab model with imposed heat flux matched the analytical temperature profile within 0.1 C. At the fluid-solid interface, integrated heat flux matched the solid-side heat transfer within 0.15% at convergence, verifying interface coupling. Coolant property spot-check against NIST REFPROP showed viscosity within 1.2% and thermal conductivity within 0.9%. No method of manufactured solutions (MMS) or published CFD benchmark comparison was reported beyond the 1-D slab test.</t>
+          <t>A conduction-only 1D slab benchmark was run and matched the analytical temperature profile within 0.1 C. Fluid-solid interface integrated heat fluxes agreed within 0.15% at convergence, verifying coupling consistency. Coolant property functions were cross-checked against NIST REFPROP at multiple temperatures (viscosity 1.2% delta, k 0.9% delta). No formal Method of Manufactured Solutions or full CFD benchmark (e.g., backward-facing step) is reported, which limits the level from 4.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2430,12 +2517,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh convergence demonstrated; residual discretization error quantified and small relative to prediction uncertainty</t>
+          <t>Mesh convergence study demonstrating acceptable grid sensitivity in quantities of interest</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three mesh levels (11.2M / 18.7M / 31.4M cells) were run at nominal conditions. T_max converged monotonically: 79.5 / 78.7 / 78.4 C. Extrapolated asymptote 78.2 C; fine-to-extrapolated difference 0.2 C (0.26%). Pressure drop changed 0.8 kPa (4.1%) from medium to fine. Mesh quality metrics reported: prism layer coverage &gt;98%, skewness &lt;0.85 only at two sharp plenum turns with no solver divergence. y+ achieved ~0.8 on fine mesh. Detailed cell counts and prism layer thicknesses documented in Appendix A.1.</t>
+          <t>Three mesh levels (coarse 11.2M, medium 18.7M, fine 31.4M cells) assessed at nominal conditions. Richardson/monotonic extrapolation yields asymptotic T_max 78.2 C; fine mesh result 78.4 C is 0.2 C (0.26%) above asymptote. Pressure drop change medium-to-fine: 0.8 kPa (4.1%). Mesh quality metrics reported (y+ ~0.8, prism layer coverage &gt;98%, skewness &lt;0.85). Detailed cell counts for fluid and solid subdomains provided in Appendix A. Quantified residual grid uncertainty is small but not expressed as a formal GCI with safety factor, keeping the level at 4 rather than 5.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2457,19 +2544,19 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Residuals reach target thresholds; energy and mass imbalance within specified limits</t>
+          <t>Evidence of adequate iterative convergence with residuals and balance checks meeting stated criteria</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Convergence criteria set at normalized residuals &lt;1e-5 for all equations, mass imbalance &lt;0.2%, energy imbalance &lt;0.1%. Energy imbalance decreased from 1.2% at 500 iterations to 0.08% at 2,000 iterations for nominal case on medium mesh. Residual histories show asymptotic decay from iteration 1,200 onward. All envelope runs achieved these criteria. Coupled pressure-velocity solver used. Reproducibility across nodes confirms solver stability.</t>
+          <t>Convergence criteria set at normalized residuals &lt;1e-5 for all equations, mass imbalance &lt;0.2%, energy imbalance &lt;0.1%. Appendix A documents residual history in three phases; energy imbalance dropped from 1.2% (500 iters) to 0.08% (2,000 iters) on the nominal medium mesh case. Interface heat flux agreement within 0.15% at convergence. Criteria met for all cases in the envelope. Detailed convergence records are archived.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2498,12 +2585,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Model setup verified by independent checks; boundary conditions and geometry documented</t>
+          <t>Evidence the model was set up correctly, including independent checks of boundary conditions, geometry, and post-processing</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Solver settings and pre-processing are scripted via STAR-CCM+ Java macros committed to version control, reducing manual setup error. File hash verification at solver launch flags any unintended input changes. Boundary conditions documented in bc_envelope.xlsx. Geometry exported from Siemens NX 2306 as Parasolid with defeature details documented. Sensitivity trials confirmed &lt;0.5 C impact of reinstating suppressed fillets. No explicit independent third-party review of model setup was reported; reproducibility across analysts or nodes is the primary use-error check.</t>
+          <t>Boundary conditions are documented and scripted; all BCs are stored in version-controlled files (bc_envelope.xlsx, powers.yaml). Die power mapping verified against test harness configuration. Geometry fidelity assessed with sensitivity trial confirming &lt;0.5 C impact from suppressed small features. File hashes verified at launch. Post-processing via scripted Python (summarize_fields.py, version-controlled). Reproducibility confirmed across two hardware nodes. No explicit independent third-party review of the model setup is documented, which limits the level.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2532,12 +2619,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equations and turbulence model selection justified; known limitations documented</t>
+          <t>Justification that the mathematical model and turbulence closure adequately represent the dominant physics for the COU</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>SST k-omega with low-Re wall treatment selected based on canonical literature for channel flows at Re ≈ 2×10⁴; rationale documented in Section 5.1. Dominant heat-flow path (die → solder → copper → TIM → aluminum → coolant) explicitly resolved. Alternative turbulence model (realizable k-ε) checked on medium mesh: T_max within 0.6–0.8 C, ΔP ~5% higher; SST retained. Known limitations documented (radiation excluded, single-value contact conductance, uniform roughness assumption, no pump spin-down). Physics regime validity boundaries stated in Section 5.8.</t>
+          <t>SST k-omega with low-Re wall treatment selected based on cited canonical literature for channel flows at Re≈2×10⁴. All dominant heat-flow paths (die→solder→copper baseplate→TIM→aluminum cold plate→coolant) are explicitly resolved. Turbulence model alternative (realizable k-ε) was checked on medium mesh: T_max differed by 0.6–0.8 C, ΔP by ~5%; SST retained with justification. Radiation and parasitic convection explicitly scoped out with physical justification. Known limitations (roughness, contact pressure distribution, single effective Hc) documented in Section 6. Temperature-dependent properties used. No formal turbulence model validation study for the specific geometry class is cited.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2566,12 +2653,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Material properties and boundary conditions from traceable, measured, or well-accepted sources with uncertainty characterized</t>
+          <t>Model inputs characterized with traceability to measurements or accepted references, with uncertainty quantification</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>TIM conductance measured in-house with guarded heat flow meter at 40/60/80 C under 0.3 MPa; σ ≈ 6.5% at 40 C; interpolated to 65 C (Hc = 14,200 W/m²-K). Aluminum conductivity from vendor cert (167±5 W/m-K) with temperature slope applied. EGW 50/50 properties from ASHRAE 2021 cross-checked against REFPROP (viscosity 1.2%, k 0.9%). Die powers from measured currents ±1% meter accuracy with 5% gate drive overhead. All input files SHA-256 hashed and version-controlled. Probabilistic uncertainty distributions assigned to all major inputs for LHS. Gap: contact pressure distribution under bolt preload represented by single effective Hc; as-built roughness not measured.</t>
+          <t>TIM conductance measured in-house with guarded heat flow meter at three temperatures and application-representative clamping (0.3 MPa); raw data and calibration certificates in lab QA folder. Aluminum k from vendor cert (167±5 W/m-K); temperature dependence applied. EGW properties from ASHRAE cross-checked against REFPROP at multiple points (&lt;1.2% delta). Die power from electrical bench with ±1% meter accuracy. Uncertainty distributions on five input classes defined and used in the LHS UQ. Mounting procedure in analysis mirrors test stack. Channel roughness not yet measured on prototype (open item), slightly limiting the level.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2593,19 +2680,19 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test article is representative of the modeled geometry; instrumentation coverage adequate</t>
+          <t>Test articles are adequately characterized and representative of the production/application geometry</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Coupon cold plate has the same channel layout as the modeled geometry. Instrumented with 12 surface thermocouples (K-type 36 AWG) at die corners plus two in-line RTDs for coolant temperature and 0–3 bar inlet/outlet pressure transducers. IR thermography used to cross-check two TC locations. Only one coupon article is reported; no statistical characterization of sample-to-sample variability or production-representativeness beyond "same channel layout" is documented. Number of specimens limited to one.</t>
+          <t>A single coupon-level cold plate with the same channel layout was used for all bench tests. Twelve surface thermocouples (K-type, 36 AWG), two RTDs, and two pressure transducers were installed. The report describes the coupon as having the same channel layout as the analysis geometry. No statistical characterization of multiple samples, no dimensional inspection (CMM) to confirm as-built geometry fidelity, and no information on production representativeness beyond the channel layout description. As-built roughness has not been measured (noted as open item). Single sample with no repeat specimens limits confidence.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2634,12 +2721,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Test conditions controlled and instrumented; measurement uncertainty documented</t>
+          <t>Test conditions well-controlled and measured with calibrated instruments; measurement uncertainties documented</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Inlet temperature controlled to ~20.0±0.3 C. Thermocouples adhered with high-temperature epoxy; bead encapsulation ~0.2 mm. Steady-state defined as dT/dt &lt; 0.05 C over 5-minute window. DAQ sampling at 2 Hz. Pressure transducers calibrated week-of-test against a DPI 620 calibrator with linearity within 0.25% FS. Emissivity set to 0.92 from black-painted witness coupon for IR comparison. Test data archived in LabData/CP-CHT/BenchA/2026Q2 with calibration sheets. Test covered three flow rates and two power levels; environment details (e.g., ambient temperature, sealed vs. open rack) not fully described.</t>
+          <t>Pressure transducers calibrated week-of-test against DPI 620 calibrator (linearity ±0.25% FS). K-type thermocouples with 36 AWG bead; emissivity set to 0.92 for IR cross-check based on black-painted witness coupon. DAQ sampling at 2 Hz; steady-state defined as dT/dt &lt;0.05 C over 5-minute window. Inlet temperature controlled to 20.0±0.3 C. Measurement uncertainty on pressure (±0.5 kPa at test point) reported. Calibration certificates referenced and stored. Test covered three flow rates and two power levels. Full uncertainty budget for thermocouple measurements (e.g., conduction error, calibration uncertainty) is not explicitly provided.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2668,12 +2755,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model boundary conditions match test conditions; input uncertainties propagated to comparison</t>
+          <t>Model inputs match test conditions with documented parameter comparison and uncertainty propagation</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Model inlet conditions (mass flow, temperature) set to match bench test nominal values. Die power per IGBT mapped to match the test harness configuration from electrical bench measurements. TIM mounting procedure in analysis mirrors test stack (same torque pattern and washers per Appendix A.4). Coolant property functions evaluated at local temperature consistent with test fluid. Probabilistic inputs include measured uncertainty distributions for inlet temperature, mass flow, and TIM conductance. Explicit side-by-side table of model vs. test input parameters not provided; some gap on as-built channel roughness and exact clamping force traceability.</t>
+          <t>Measured inlet temperature (20.0±0.3 C) and flow rates (0.09, 0.12, 0.16 kg/s) are directly applied as model boundary conditions. Die power mapping confirmed consistent with test harness. TIM conductance interpolated at test-representative temperature and clamping. Mounting procedure (torque pattern and washers) mirrored in analysis. Uncertainty on inlet temperature and flow rate explicitly included in LHS. Channel roughness in model (10 μm uniform) is an assumption not validated against as-built coupon, which is a noted gap. Boundary condition file hashes ensure exact correspondence between runs.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2698,16 +2785,16 @@
         <v>3</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of model predictions to measurements with uncertainty bounds at multiple operating points</t>
+          <t>Quantitative comparison of model predictions to experimental data with error metrics and uncertainty bands</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Temperature: average absolute difference 1.9 C, maximum 3.4 C at six die corners at 450 W nominal; 2.3 C overprediction at 300 W/0.09 kg/s, &lt;1.5 C average at 0.16 kg/s. Pressure drop: 18.7 vs. 19.6±0.5 kPa (4.6% low) at nominal. Probabilistic LHS provides output uncertainty bands: mean T_max 78.9 C, σ = 0.95 C, 90th percentile 81.1 C; ΔP 90th percentile 20.3 kPa. Sobol sensitivity indices quantify dominant input contributors. Comparison across six spatial locations and three test conditions. Gap: 600 W and off-nominal inlet temperatures not yet bench-validated.</t>
+          <t>Temperature: average absolute error 1.9 C across six die-corner TCs at nominal (450 W, 0.12 kg/s); maximum single-point deviation 3.4 C. Comparisons made at three flow rates and two power levels (six test conditions total). Pressure drop: 4.6% underprediction at nominal. IR thermography used to cross-check two TC locations. Measurement uncertainty on pressure (±0.5 kPa) reported. Probabilistic 90th-percentile prediction envelope quantified (T_max 90th: 81.1 C). Formal statistical validation metrics (e.g., MAPE, correlation coefficient, u-pooled metric) are not reported; coverage of 600 W and off-nominal inlet temperatures is not yet available.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2736,12 +2823,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs (peak junction temperature, pressure drop) directly address the design decision and are measurable both computationally and experimentally</t>
+          <t>Model outputs directly address the safety/performance quantities needed for the decision</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Peak die junction temperature (T_max) directly governs IGBT reliability and thermal guardband setting; coolant-side pressure drop directly governs pump sizing. Both QoIs are computed as primary model outputs and measured directly by thermocouples/RTDs and calibrated pressure transducers in the bench test. Sensitivity analysis confirms T_max is dominated by inlet temperature control (61% Sobol index), making the model directly actionable for guardband specification. Probabilistic outputs (90th percentile values) are mapped to design use in Section 7.</t>
+          <t>Peak die junction temperature (T_max) and coolant-side pressure drop (ΔP) are explicitly the two quantities needed to set thermal guardbands and size the pump. Both QoIs are computed by the model, measured in the bench test, and used directly in the decision (guardbands in Section 7). Sensitivity and probabilistic analyses quantify the influence of each input on both QoIs, directly supporting risk-based design decisions. The mapping from model output to decision criterion is clearly stated.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2766,16 +2853,16 @@
         <v>3</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions cover the intended operating envelope; gaps identified and bounded</t>
+          <t>Validation conditions cover the intended operating envelope including geometry, power levels, flow rates, and inlet temperatures</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation performed at the same channel geometry, same fluid, same clamping procedure, and same nominal operating point (0.12 kg/s, 20 C inlet) as the COU. Three flow rates (0.09, 0.12, 0.16 kg/s) and two power levels (300, 450 W) tested. Gaps explicitly identified and documented: 600 W case not yet bench-validated; inlet temperatures outside ~20 C not tested; as-built roughness unmeasured; off-nominal coolant compositions excluded. Planned actions to close gaps stated (next thermal bench slot, mid Q4). Local sensitivity and LHS bound the extrapolation uncertainty quantitatively.</t>
+          <t>Validation was performed on a coupon with the same channel layout at 300 W and 450 W (two of three load cases) and three flow rates within the 0.08–0.20 kg/s range, all at ~20 C inlet. The 600 W load case is within the COU scope but has not been bench-verified. Inlet temperatures of 10 C and 35 C (COU boundary conditions) have not been tested. Section 5.8 explicitly documents these gaps and notes plans for the next bench window. Geometry is representative (same channel layout) but as-built dimensional verification is absent. The partial coverage of the COU envelope, particularly the absence of the highest power case and inlet temperature extremes, limits the achieved level.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2960,7 +3047,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The CP-CHT-v1.6 model predicts peak junction temperature within ~2 C average (maximum 3.4 C) and pressure drop within ~5% of bench measurements across all validated operating points. Mesh discretization error is small (0.26% on T_max at fine level), solver convergence is well-documented, and input data are traceable to measured or widely accepted sources with probabilistic uncertainty characterization. Sensitivity and LHS analyses quantify dominant uncertainty contributors and support the stated design use (pump sizing, thermal guardband setting). The model is accepted for early design trades on channel geometry and preliminary pump sizing within the exercised envelope (300–450 W, 0.09–0.16 kg/s, ~20 C inlet). Acceptance is conditioned on: (1) noting that the 600 W case and off-nominal inlet temperatures (10–35 C range outside ~20 C) carry higher uncertainty until the planned additional bench tests are completed; (2) applying the recommended 2.5 C margin on T_max predictions and 10% margin on pressure drop for manufacturing variability; and (3) revisiting roughness assumptions and TIM contact pressure representation when as-built profilometry and fastener torque curves become available.</t>
+          <t>Within the exercised envelope (300–450 W, 0.09–0.16 kg/s, ~20 C inlet), the CP-CHT-v1.6 model meets its stated accuracy targets: junction temperature predictions within ~2 C average (max 3.4 C) and pressure drop within ~5% of bench measurements. Mesh sensitivity is small (0.26% T_max, fine-to-extrapolated), solver convergence is tight (residuals &lt;1e-5, energy imbalance 0.08%), and input data are traceable to measurements with quantified uncertainties. A 200-sample LHS UQ provides a probabilistic prediction envelope. The model is accepted for early design trades on channel geometry and preliminary pump sizing. Acceptance carries the following conditions: (1) the 600 W case and 10 C / 35 C inlet temperature cases must be bench-verified before using model predictions at those conditions as design commitments; (2) as-built channel roughness should be measured on the prototype to tighten ΔP predictions; (3) clamp force vs torque data should be acquired to refine TIM contact conductance representation. These open items are documented in Section 6 and Appendix A.8.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
